--- a/Project/outputs/tables/table_gru_metrics_h10.xlsx
+++ b/Project/outputs/tables/table_gru_metrics_h10.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008730385452508926</v>
+        <v>0.009471473284065723</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04906395450234413</v>
+        <v>0.04981121048331261</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09343653168064901</v>
+        <v>0.09732149446070854</v>
       </c>
       <c r="E2" t="n">
-        <v>29.28156852722168</v>
+        <v>28.66546440124512</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4703632887189292</v>
+        <v>0.4818355640535373</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004368327092379332</v>
+        <v>0.004579755943268538</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04465679824352264</v>
+        <v>0.04345269873738289</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06609332108752995</v>
+        <v>0.06767389410451077</v>
       </c>
       <c r="E3" t="n">
-        <v>34.62775421142578</v>
+        <v>25.51492118835449</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4684512428298279</v>
+        <v>0.4894837476099426</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004303745925426483</v>
+        <v>0.005694420076906681</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04111498966813087</v>
+        <v>0.05340755358338356</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06560294143882943</v>
+        <v>0.07546138136097616</v>
       </c>
       <c r="E4" t="n">
-        <v>24.30929565429688</v>
+        <v>35.52923965454102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.502868068833652</v>
+        <v>0.4608030592734226</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004953767172992229</v>
+        <v>0.003715099534019828</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04931716248393059</v>
+        <v>0.03733495622873306</v>
       </c>
       <c r="D5" t="n">
-        <v>0.070383003438275</v>
+        <v>0.06095161633640102</v>
       </c>
       <c r="E5" t="n">
-        <v>32.29343795776367</v>
+        <v>22.62378120422363</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4665391969407266</v>
+        <v>0.4952198852772466</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002469917759299278</v>
+        <v>0.001892426516860723</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03791684284806252</v>
+        <v>0.03208820149302483</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04969826716596142</v>
+        <v>0.04350202888211909</v>
       </c>
       <c r="E6" t="n">
-        <v>22.23349380493164</v>
+        <v>17.96870231628418</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5239005736137667</v>
+        <v>0.51434034416826</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001931483973748982</v>
+        <v>0.003528890665620565</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03415055200457573</v>
+        <v>0.04237909615039825</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04394865155780075</v>
+        <v>0.05940446671438575</v>
       </c>
       <c r="E7" t="n">
-        <v>17.15029335021973</v>
+        <v>22.80908012390137</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5200764818355641</v>
+        <v>0.4416826003824092</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007062698248773813</v>
+        <v>0.002502556890249252</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0584256686270237</v>
+        <v>0.03840279579162598</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08403986107064798</v>
+        <v>0.05002556236814587</v>
       </c>
       <c r="E8" t="n">
-        <v>30.32930755615234</v>
+        <v>19.92326736450195</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4627151051625239</v>
+        <v>0.4837476099426386</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002226803917437792</v>
+        <v>0.002421005163341761</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0325813814997673</v>
+        <v>0.03720632568001747</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04718902327276749</v>
+        <v>0.04920371086962609</v>
       </c>
       <c r="E9" t="n">
-        <v>17.06634140014648</v>
+        <v>25.51334762573242</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5219885277246654</v>
+        <v>0.4703632887189292</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004505891192820854</v>
+        <v>0.004225703509291634</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04340341873466969</v>
+        <v>0.04176035476848483</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06504895008905762</v>
+        <v>0.06294301938710917</v>
       </c>
       <c r="E10" t="n">
-        <v>25.91143608093262</v>
+        <v>24.8184757232666</v>
       </c>
       <c r="F10" t="n">
-        <v>0.492112810707457</v>
+        <v>0.4796845124282982</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.002280984772369266</v>
+        <v>0.003424738999456167</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02922837994992733</v>
+        <v>0.03764532506465912</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04775965632591241</v>
+        <v>0.05852126963298188</v>
       </c>
       <c r="E11" t="n">
-        <v>17.59088706970215</v>
+        <v>20.73755073547363</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5141318977119784</v>
+        <v>0.5162162162162162</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.001953286118805408</v>
+        <v>0.001669189892709255</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03203675523400307</v>
+        <v>0.02897686697542667</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04419599663776583</v>
+        <v>0.04085572044046287</v>
       </c>
       <c r="E12" t="n">
-        <v>28.47769165039062</v>
+        <v>19.84578132629395</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4831763122476447</v>
+        <v>0.4878378378378379</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.001644704607315361</v>
+        <v>0.001891960157081485</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02798908017575741</v>
+        <v>0.03245405480265617</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04055495786356289</v>
+        <v>0.0434966683446156</v>
       </c>
       <c r="E13" t="n">
-        <v>28.36215591430664</v>
+        <v>24.96767044067383</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4845222072678331</v>
+        <v>0.504054054054054</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002999309916049242</v>
+        <v>0.00161881628446281</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04159801080822945</v>
+        <v>0.02892180345952511</v>
       </c>
       <c r="D14" t="n">
-        <v>0.05476595581243189</v>
+        <v>0.04023451608336814</v>
       </c>
       <c r="E14" t="n">
-        <v>31.52014923095703</v>
+        <v>30.06549263000488</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4993270524899058</v>
+        <v>0.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.006927660666406155</v>
+        <v>0.007152902893722057</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04404343292117119</v>
+        <v>0.04656583070755005</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08323256974529955</v>
+        <v>0.08457483605495229</v>
       </c>
       <c r="E15" t="n">
-        <v>21.3338737487793</v>
+        <v>21.08169555664062</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4804845222072678</v>
+        <v>0.504054054054054</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.006312990561127663</v>
+        <v>0.004227615892887115</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05404342710971832</v>
+        <v>0.04441003501415253</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07945433003384814</v>
+        <v>0.06502011913928731</v>
       </c>
       <c r="E16" t="n">
-        <v>21.01872444152832</v>
+        <v>23.62056159973145</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5343203230148048</v>
+        <v>0.5216216216216216</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.003818029770627618</v>
+        <v>0.005316257011145353</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04609166458249092</v>
+        <v>0.04708387702703476</v>
       </c>
       <c r="D17" t="n">
-        <v>0.06179020772442522</v>
+        <v>0.07291266701434912</v>
       </c>
       <c r="E17" t="n">
-        <v>30.23498344421387</v>
+        <v>18.39607048034668</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4724091520861373</v>
+        <v>0.5445945945945946</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002455126261338592</v>
+        <v>0.003119273344054818</v>
       </c>
       <c r="C18" t="n">
-        <v>0.03244494274258614</v>
+        <v>0.04334477335214615</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04954923068362002</v>
+        <v>0.05585045518216318</v>
       </c>
       <c r="E18" t="n">
-        <v>23.12820434570312</v>
+        <v>35.57369613647461</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4966352624495289</v>
+        <v>0.4702702702702703</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.003549011584254913</v>
+        <v>0.003552594309439883</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03843446169048548</v>
+        <v>0.03867532080039382</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05766286310335824</v>
+        <v>0.05768328148652255</v>
       </c>
       <c r="E19" t="n">
-        <v>25.20833396911621</v>
+        <v>24.28606414794922</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4956258411843876</v>
+        <v>0.5060810810810811</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
